--- a/04 Daily_Settlement_Review/assets/2026-05-27日性能记录表格.xlsx
+++ b/04 Daily_Settlement_Review/assets/2026-05-27日性能记录表格.xlsx
@@ -1,24 +1,82 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\DataWork\Storage_Strategy\04 Daily_Settlement_Review\assets\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{851D27EC-EC9E-4D06-B73B-292F4C9EAF2F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8892" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
     <sheet name="SheetJS" sheetId="1" r:id="rId1"/>
   </sheets>
+  <calcPr calcId="191029"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="12">
+  <si>
+    <t>日期</t>
+  </si>
+  <si>
+    <t>小时</t>
+  </si>
+  <si>
+    <t>电站名称</t>
+  </si>
+  <si>
+    <t>AGC K1</t>
+  </si>
+  <si>
+    <t>AGC K2</t>
+  </si>
+  <si>
+    <t>AGC K3</t>
+  </si>
+  <si>
+    <t>综合性能指标(Kp)</t>
+  </si>
+  <si>
+    <t>调节深度(MW)</t>
+  </si>
+  <si>
+    <t>2026-05-27</t>
+  </si>
+  <si>
+    <t>苏留润津储能</t>
+  </si>
+  <si>
+    <t>中标价</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>收入</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -46,10 +104,18 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -374,53 +440,60 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H6"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:K7"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>日期</v>
-      </c>
-      <c r="B1" t="str">
-        <v>小时</v>
-      </c>
-      <c r="C1" t="str">
-        <v>电站名称</v>
-      </c>
-      <c r="D1" t="str">
-        <v>AGC K1</v>
-      </c>
-      <c r="E1" t="str">
-        <v>AGC K2</v>
-      </c>
-      <c r="F1" t="str">
-        <v>AGC K3</v>
-      </c>
-      <c r="G1" t="str">
-        <v>综合性能指标(Kp)</v>
-      </c>
-      <c r="H1" t="str">
-        <v>调节深度(MW)</v>
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" t="s">
+        <v>10</v>
+      </c>
+      <c r="K1" t="s">
+        <v>11</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>2026-05-27</v>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>8</v>
       </c>
       <c r="B2">
         <v>9</v>
       </c>
-      <c r="C2" t="str">
-        <v>苏留润津储能</v>
+      <c r="C2" t="s">
+        <v>9</v>
       </c>
       <c r="D2">
         <v>1.3</v>
       </c>
       <c r="E2">
-        <v>1.766441</v>
+        <v>1.7664409999999999</v>
       </c>
       <c r="F2">
-        <v>1.585311</v>
+        <v>1.5853109999999999</v>
       </c>
       <c r="G2">
         <v>1.833658</v>
@@ -428,51 +501,65 @@
       <c r="H2">
         <v>203.29</v>
       </c>
+      <c r="J2">
+        <v>5.97</v>
+      </c>
+      <c r="K2">
+        <f>J2*H2*G2</f>
+        <v>2225.4030788753998</v>
+      </c>
     </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>2026-05-27</v>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>8</v>
       </c>
       <c r="B3">
         <v>11</v>
       </c>
-      <c r="C3" t="str">
-        <v>苏留润津储能</v>
+      <c r="C3" t="s">
+        <v>9</v>
       </c>
       <c r="D3">
         <v>1.3</v>
       </c>
       <c r="E3">
-        <v>1.74537</v>
+        <v>1.7453700000000001</v>
       </c>
       <c r="F3">
-        <v>1.554321</v>
+        <v>1.5543210000000001</v>
       </c>
       <c r="G3">
-        <v>1.816998</v>
+        <v>1.8169979999999999</v>
       </c>
       <c r="H3">
         <v>203.51</v>
       </c>
+      <c r="J3">
+        <v>8</v>
+      </c>
+      <c r="K3">
+        <f t="shared" ref="K3:K6" si="0">J3*H3*G3</f>
+        <v>2958.2181038399999</v>
+      </c>
     </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>2026-05-27</v>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>8</v>
       </c>
       <c r="B4">
         <v>14</v>
       </c>
-      <c r="C4" t="str">
-        <v>苏留润津储能</v>
+      <c r="C4" t="s">
+        <v>9</v>
       </c>
       <c r="D4">
         <v>1.3</v>
       </c>
       <c r="E4">
-        <v>1.740784</v>
+        <v>1.7407840000000001</v>
       </c>
       <c r="F4">
-        <v>1.613072</v>
+        <v>1.6130720000000001</v>
       </c>
       <c r="G4">
         <v>1.830384</v>
@@ -480,25 +567,32 @@
       <c r="H4">
         <v>182.65</v>
       </c>
+      <c r="J4">
+        <v>5.97</v>
+      </c>
+      <c r="K4">
+        <f t="shared" si="0"/>
+        <v>1995.888236472</v>
+      </c>
     </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>2026-05-27</v>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>8</v>
       </c>
       <c r="B5">
         <v>18</v>
       </c>
-      <c r="C5" t="str">
-        <v>苏留润津储能</v>
+      <c r="C5" t="s">
+        <v>9</v>
       </c>
       <c r="D5">
         <v>1.3</v>
       </c>
       <c r="E5">
-        <v>1.742903</v>
+        <v>1.7429030000000001</v>
       </c>
       <c r="F5">
-        <v>1.591398</v>
+        <v>1.5913980000000001</v>
       </c>
       <c r="G5">
         <v>1.82562</v>
@@ -506,25 +600,32 @@
       <c r="H5">
         <v>221.87</v>
       </c>
+      <c r="J5">
+        <v>5.97</v>
+      </c>
+      <c r="K5">
+        <f t="shared" si="0"/>
+        <v>2418.1503471179999</v>
+      </c>
     </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>2026-05-27</v>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>8</v>
       </c>
       <c r="B6">
         <v>23</v>
       </c>
-      <c r="C6" t="str">
-        <v>苏留润津储能</v>
+      <c r="C6" t="s">
+        <v>9</v>
       </c>
       <c r="D6">
         <v>1.3</v>
       </c>
       <c r="E6">
-        <v>1.784839</v>
+        <v>1.7848390000000001</v>
       </c>
       <c r="F6">
-        <v>1.588172</v>
+        <v>1.5881719999999999</v>
       </c>
       <c r="G6">
         <v>1.84192</v>
@@ -532,10 +633,37 @@
       <c r="H6">
         <v>235.22</v>
       </c>
+      <c r="J6">
+        <v>5.97</v>
+      </c>
+      <c r="K6">
+        <f t="shared" si="0"/>
+        <v>2586.540841728</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="G7">
+        <f>AVERAGE(G2:G6)</f>
+        <v>1.8297159999999999</v>
+      </c>
+      <c r="H7">
+        <f>AVERAGE(H2:H6)</f>
+        <v>209.30799999999999</v>
+      </c>
+      <c r="J7">
+        <f>AVERAGE(J2:J6)</f>
+        <v>6.3759999999999994</v>
+      </c>
+      <c r="K7">
+        <f>SUM(K2:K6)</f>
+        <v>12184.200608033399</v>
+      </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H6"/>
+    <ignoredError sqref="A1:H6" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>